--- a/practice/answers/s1_q05.xlsx
+++ b/practice/answers/s1_q05.xlsx
@@ -18,7 +18,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -42,8 +42,8 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -51,15 +51,15 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
       <name val="Consolas"/>
       <color rgb="002F5D46"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0024302A"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -76,12 +76,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6EFD9"/>
+        <fgColor rgb="004A7C59"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A7C59"/>
+        <fgColor rgb="00F6EFD9"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,32 +97,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -488,27 +494,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="3" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Q5 — Where the brackets go</t>
+          <t>Weighted average — the farm's real average yield</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Four ways of writing the same intended calculation: revenue per acre after a $40/ac input cost, times the acres. Only one is right.</t>
+          <t>The plain mean of the yield column treats every field as equally important. Weighting by acres counts every bushel once, which is what 'the average across the farm' means.</t>
         </is>
       </c>
     </row>
@@ -516,155 +522,201 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Acres</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
           <t>Yield (bu/ac)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Bushels</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>The formula in D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="C5" s="7" t="n">
         <v>41.2</v>
       </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Price ($/bu)</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>14.2</v>
+      <c r="D5" s="8">
+        <f>B5*C5</f>
+        <v/>
+      </c>
+      <c r="E5" s="9">
+        <f>_xlfn.FORMULATEXT(D5)</f>
+        <v/>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Cost ($/ac)</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>40</v>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>240</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="D6" s="8">
+        <f>B6*C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="9">
+        <f>_xlfn.FORMULATEXT(D6)</f>
+        <v/>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Acres</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Creek</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1"/>
+        <v>95</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="D7" s="8">
+        <f>B7*C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="9">
+        <f>_xlfn.FORMULATEXT(D7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>310</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="D8" s="8">
+        <f>B8*C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="9">
+        <f>_xlfn.FORMULATEXT(D8)</f>
+        <v/>
+      </c>
+    </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="inlineStr"/>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Formula</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Right?</t>
-        </is>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Rented</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="D9" s="8">
+        <f>B9*C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="9">
+        <f>_xlfn.FORMULATEXT(D9)</f>
+        <v/>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="B10" s="9">
-        <f>(B4*B5-B6)*B7</f>
-        <v/>
-      </c>
-      <c r="C10" s="10">
-        <f>_xlfn.FORMULATEXT(B10)</f>
-        <v/>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>Net per acre first, then scaled by acres.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>No brackets</t>
-        </is>
-      </c>
-      <c r="B11" s="9">
-        <f>B4*B5-B6*B7</f>
-        <v/>
-      </c>
-      <c r="C11" s="10">
-        <f>_xlfn.FORMULATEXT(B11)</f>
-        <v/>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>Excel multiplies before subtracting, so this subtracts the whole cost bill from per-acre revenue.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B10" s="11">
+        <f>SUM(B5:B9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="12">
+        <f>SUM(D5:D9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1"/>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Brackets in the wrong place</t>
-        </is>
-      </c>
-      <c r="B12" s="9">
-        <f>B4*(B5-B6)*B7</f>
-        <v/>
-      </c>
-      <c r="C12" s="10">
-        <f>_xlfn.FORMULATEXT(B12)</f>
-        <v/>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>Subtracts the cost from the PRICE, not from the revenue.</t>
-        </is>
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Plain mean of the yields</t>
+        </is>
+      </c>
+      <c r="C12" s="13">
+        <f>AVERAGE(C5:C9)</f>
+        <v/>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>Cost applied twice</t>
-        </is>
-      </c>
-      <c r="B13" s="9">
-        <f>(B4*B5-B6)*B7-B6</f>
-        <v/>
-      </c>
-      <c r="C13" s="10">
-        <f>_xlfn.FORMULATEXT(B13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>Charges the input cost again on top.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1"/>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>The correct answer is $65,405 -- (41.2 x $14.20 - $40) x 120. PEMDAS means multiplication happens before subtraction unless brackets say otherwise.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1"/>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Weighted: bushels / acres</t>
+        </is>
+      </c>
+      <c r="C13" s="13">
+        <f>D10/B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Weighted: SUMPRODUCT</t>
+        </is>
+      </c>
+      <c r="C14" s="13">
+        <f>SUMPRODUCT(C5:C9,B5:B9)/SUM(B5:B9)</f>
+        <v/>
+      </c>
+      <c r="D14" s="9">
+        <f>_xlfn.FORMULATEXT(C14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1"/>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>40.1 against 39.0. The 95-acre Creek field is the best of the five and the 310-acre Home field the worst, so counting fields equally flatters the farm. The two weighted routes agree, which is the check: if they disagree, one is wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A15:E15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/practice/answers/s1_q05.xlsx
+++ b/practice/answers/s1_q05.xlsx
@@ -97,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -126,6 +126,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -494,13 +497,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -549,14 +552,14 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Willow</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>120</v>
+        <v>213</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>41.2</v>
+        <v>52.4</v>
       </c>
       <c r="D5" s="8">
         <f>B5*C5</f>
@@ -570,14 +573,14 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>240</v>
+        <v>147</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>38.6</v>
+        <v>61.8</v>
       </c>
       <c r="D6" s="8">
         <f>B6*C6</f>
@@ -591,14 +594,14 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Creek</t>
+          <t>Slough</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>95</v>
+        <v>326</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>44.8</v>
+        <v>47.9</v>
       </c>
       <c r="D7" s="8">
         <f>B7*C7</f>
@@ -612,14 +615,14 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Quarter</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>310</v>
+        <v>89</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>36.1</v>
+        <v>64.5</v>
       </c>
       <c r="D8" s="8">
         <f>B8*C8</f>
@@ -633,14 +636,14 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Rented</t>
+          <t>Airport</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>175</v>
+        <v>255</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>39.9</v>
+        <v>55.2</v>
       </c>
       <c r="D9" s="8">
         <f>B9*C9</f>
@@ -677,6 +680,15 @@
         <f>AVERAGE(C5:C9)</f>
         <v/>
       </c>
+      <c r="D12" s="14">
+        <f>COUNT(C5:C9)</f>
+        <v/>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>fields averaged</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
@@ -705,18 +717,163 @@
       </c>
     </row>
     <row r="15" ht="18" customHeight="1"/>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>40.1 against 39.0. The 95-acre Creek field is the best of the five and the 310-acre Home field the worst, so counting fields equally flatters the farm. The two weighted routes agree, which is the check: if they disagree, one is wrong.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1"/>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Rounding vs formatting</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Bushels</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>ROUND to whole</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>The formula in C</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Willow</t>
+        </is>
+      </c>
+      <c r="B18" s="8">
+        <f>B5*C5</f>
+        <v/>
+      </c>
+      <c r="C18" s="14">
+        <f>ROUND(B5*C5,0)</f>
+        <v/>
+      </c>
+      <c r="D18" s="9">
+        <f>_xlfn.FORMULATEXT(C18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="B19" s="8">
+        <f>B6*C6</f>
+        <v/>
+      </c>
+      <c r="C19" s="14">
+        <f>ROUND(B6*C6,0)</f>
+        <v/>
+      </c>
+      <c r="D19" s="9">
+        <f>_xlfn.FORMULATEXT(C19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Slough</t>
+        </is>
+      </c>
+      <c r="B20" s="8">
+        <f>B7*C7</f>
+        <v/>
+      </c>
+      <c r="C20" s="14">
+        <f>ROUND(B7*C7,0)</f>
+        <v/>
+      </c>
+      <c r="D20" s="9">
+        <f>_xlfn.FORMULATEXT(C20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="B21" s="8">
+        <f>B8*C8</f>
+        <v/>
+      </c>
+      <c r="C21" s="14">
+        <f>ROUND(B8*C8,0)</f>
+        <v/>
+      </c>
+      <c r="D21" s="9">
+        <f>_xlfn.FORMULATEXT(C21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Airport</t>
+        </is>
+      </c>
+      <c r="B22" s="8">
+        <f>B9*C9</f>
+        <v/>
+      </c>
+      <c r="C22" s="14">
+        <f>ROUND(B9*C9,0)</f>
+        <v/>
+      </c>
+      <c r="D22" s="9">
+        <f>_xlfn.FORMULATEXT(C22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B23" s="12">
+        <f>SUM(B18:B22)</f>
+        <v/>
+      </c>
+      <c r="C23" s="11">
+        <f>SUM(C18:C22)</f>
+        <v/>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>half a bushel apart</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1"/>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>56.4 against 54.1. The 89-acre Quarter field is the best of the five and the 326-acre Slough field the worst, so counting fields equally flatters the farm. The two weighted routes agree, which is the check: if they disagree, one is wrong. Below, ROUND changes the stored bushels, so the rounded column really does total what it displays -- a formatted column would still add up its unrounded values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A25:E25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/practice/answers/s1_q05.xlsx
+++ b/practice/answers/s1_q05.xlsx
@@ -857,7 +857,7 @@
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>half a bushel apart</t>
+          <t>0.3 bushels apart</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>56.4 against 54.1. The 89-acre Quarter field is the best of the five and the 326-acre Slough field the worst, so counting fields equally flatters the farm. The two weighted routes agree, which is the check: if they disagree, one is wrong. Below, ROUND changes the stored bushels, so the rounded column really does total what it displays -- a formatted column would still add up its unrounded values.</t>
+          <t>56.4 against 54.1. The 89-acre Quarter field is the best of the five and the 326-acre Slough field the worst, so counting fields equally flatters the farm. The two weighted routes agree, which is the check: if they disagree, one is wrong. Below, ROUND changes the stored bushels, so the rounded column really does total what it displays -- a formatted column would still add up its unrounded values. Quarter lands on exactly 5,740.5, and Excel rounds a half away from zero.</t>
         </is>
       </c>
     </row>

--- a/practice/answers/s1_q05.xlsx
+++ b/practice/answers/s1_q05.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,45 +29,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="004A7C59"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="002F5D46"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -76,12 +41,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A7C59"/>
+        <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6EFD9"/>
+        <fgColor rgb="00D9D2E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE5CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,41 +82,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -497,383 +472,328 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Weighted average — the farm's real average yield</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>The plain mean of the yield column treats every field as equally important. Weighting by acres counts every bushel once, which is what 'the average across the farm' means.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Acres</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Yield (bu/ac)</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Bushels</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>The formula in D</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Bushels (ROUND)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Willow</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B2" s="4" t="n">
         <v>213</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C2" s="5" t="n">
         <v>52.4</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D2" s="6">
+        <f>B2*C2</f>
+        <v/>
+      </c>
+      <c r="E2" s="7">
+        <f>ROUND(B2*C2,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>147</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="D3" s="6">
+        <f>B3*C3</f>
+        <v/>
+      </c>
+      <c r="E3" s="7">
+        <f>ROUND(B3*C3,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Slough</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>326</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="D4" s="6">
+        <f>B4*C4</f>
+        <v/>
+      </c>
+      <c r="E4" s="7">
+        <f>ROUND(B4*C4,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="D5" s="6">
         <f>B5*C5</f>
         <v/>
       </c>
-      <c r="E5" s="9">
-        <f>_xlfn.FORMULATEXT(D5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>147</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="D6" s="8">
+      <c r="E5" s="7">
+        <f>ROUND(B5*C5,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Airport</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>255</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="D6" s="6">
         <f>B6*C6</f>
         <v/>
       </c>
-      <c r="E6" s="9">
-        <f>_xlfn.FORMULATEXT(D6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Slough</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>326</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="D7" s="8">
-        <f>B7*C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="9">
-        <f>_xlfn.FORMULATEXT(D7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Quarter</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>89</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="D8" s="8">
-        <f>B8*C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="9">
-        <f>_xlfn.FORMULATEXT(D8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Airport</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>255</v>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="D9" s="8">
-        <f>B9*C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="9">
-        <f>_xlfn.FORMULATEXT(D9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="E6" s="7">
+        <f>ROUND(B6*C6,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B10" s="11">
-        <f>SUM(B5:B9)</f>
-        <v/>
-      </c>
-      <c r="D10" s="12">
-        <f>SUM(D5:D9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1"/>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Plain mean of the yields</t>
-        </is>
-      </c>
-      <c r="C12" s="13">
-        <f>AVERAGE(C5:C9)</f>
-        <v/>
-      </c>
-      <c r="D12" s="14">
-        <f>COUNT(C5:C9)</f>
-        <v/>
-      </c>
-      <c r="E12" s="15" t="inlineStr">
-        <is>
-          <t>fields averaged</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Weighted: bushels / acres</t>
-        </is>
-      </c>
-      <c r="C13" s="13">
-        <f>D10/B10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Weighted: SUMPRODUCT</t>
-        </is>
-      </c>
-      <c r="C14" s="13">
-        <f>SUMPRODUCT(C5:C9,B5:B9)/SUM(B5:B9)</f>
-        <v/>
-      </c>
-      <c r="D14" s="9">
-        <f>_xlfn.FORMULATEXT(C14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1"/>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>Rounding vs formatting</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Bushels</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>ROUND to whole</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>The formula in C</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Willow</t>
-        </is>
-      </c>
-      <c r="B18" s="8">
-        <f>B5*C5</f>
-        <v/>
-      </c>
-      <c r="C18" s="14">
-        <f>ROUND(B5*C5,0)</f>
-        <v/>
-      </c>
-      <c r="D18" s="9">
-        <f>_xlfn.FORMULATEXT(C18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="B19" s="8">
-        <f>B6*C6</f>
-        <v/>
-      </c>
-      <c r="C19" s="14">
-        <f>ROUND(B6*C6,0)</f>
-        <v/>
-      </c>
-      <c r="D19" s="9">
-        <f>_xlfn.FORMULATEXT(C19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Slough</t>
-        </is>
-      </c>
-      <c r="B20" s="8">
-        <f>B7*C7</f>
-        <v/>
-      </c>
-      <c r="C20" s="14">
-        <f>ROUND(B7*C7,0)</f>
-        <v/>
-      </c>
-      <c r="D20" s="9">
-        <f>_xlfn.FORMULATEXT(C20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Quarter</t>
-        </is>
-      </c>
-      <c r="B21" s="8">
-        <f>B8*C8</f>
-        <v/>
-      </c>
-      <c r="C21" s="14">
-        <f>ROUND(B8*C8,0)</f>
-        <v/>
-      </c>
-      <c r="D21" s="9">
-        <f>_xlfn.FORMULATEXT(C21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Airport</t>
-        </is>
-      </c>
-      <c r="B22" s="8">
-        <f>B9*C9</f>
-        <v/>
-      </c>
-      <c r="C22" s="14">
-        <f>ROUND(B9*C9,0)</f>
-        <v/>
-      </c>
-      <c r="D22" s="9">
-        <f>_xlfn.FORMULATEXT(C22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B23" s="12">
-        <f>SUM(B18:B22)</f>
-        <v/>
-      </c>
-      <c r="C23" s="11">
-        <f>SUM(C18:C22)</f>
-        <v/>
-      </c>
-      <c r="D23" s="15" t="inlineStr">
-        <is>
-          <t>0.3 bushels apart</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1"/>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>56.4 against 54.1. The 89-acre Quarter field is the best of the five and the 326-acre Slough field the worst, so counting fields equally flatters the farm. The two weighted routes agree, which is the check: if they disagree, one is wrong. Below, ROUND changes the stored bushels, so the rounded column really does total what it displays -- a formatted column would still add up its unrounded values. Quarter lands on exactly 5,740.5, and Excel rounds a half away from zero.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1"/>
+      <c r="B7" s="8">
+        <f>SUM(B2:B6)</f>
+        <v/>
+      </c>
+      <c r="D7" s="6">
+        <f>SUM(D2:D6)</f>
+        <v/>
+      </c>
+      <c r="E7" s="7">
+        <f>SUM(E2:E6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Mean yield (AVERAGE)</t>
+        </is>
+      </c>
+      <c r="B9" s="10">
+        <f>AVERAGE(C2:C6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>COUNT of fields</t>
+        </is>
+      </c>
+      <c r="B10" s="9">
+        <f>COUNT(C2:C6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Weighted average (bu/ac)</t>
+        </is>
+      </c>
+      <c r="B11" s="12">
+        <f>D7/B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>SUMPRODUCT over SUM</t>
+        </is>
+      </c>
+      <c r="B12" s="14">
+        <f>SUMPRODUCT(C2:C6,B2:B6)/SUM(B2:B6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>The rounded column totals 55,678 -- 0.3 bushels above the unrounded 55,677.7 (Quarter lands on exactly 5,740.5 and rounds up). ROUND changes the stored values, so the total is a sum of rounded numbers; formatting to zero decimals only changes the display, so the column still totals its unrounded values.</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="16" t="n"/>
+      <c r="G14" s="16" t="n"/>
+      <c r="H14" s="16" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="n"/>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="16" t="n"/>
+      <c r="G15" s="16" t="n"/>
+      <c r="H15" s="16" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="n"/>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="16" t="n"/>
+      <c r="G16" s="16" t="n"/>
+      <c r="H16" s="16" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>The weighted average answers it: it counts every bushel once regardless of which field grew it. The plain mean treats each field as equally important, so the small, high-yielding Quarter field counts as much as the large Slough field and pulls the answer up by about 2.3 bu/ac.</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
+      <c r="F18" s="18" t="n"/>
+      <c r="G18" s="18" t="n"/>
+      <c r="H18" s="18" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="n"/>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="18" t="n"/>
+      <c r="G19" s="18" t="n"/>
+      <c r="H19" s="18" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="n"/>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
+      <c r="F20" s="18" t="n"/>
+      <c r="G20" s="18" t="n"/>
+      <c r="H20" s="18" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Part (a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>Part (b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Part (c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Part (d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>Part (e)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>Part (f)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A14:H16"/>
+    <mergeCell ref="A18:H20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/practice/answers/s1_q05.xlsx
+++ b/practice/answers/s1_q05.xlsx
@@ -1,72 +1,164 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr/>
-  <workbookProtection/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_884D7FDFD678FCDF641508F456866EBD97B8E4A7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77F50373-C91B-4781-AB13-BBAE9F1CEF75}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Answer" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Acres</t>
+  </si>
+  <si>
+    <t>Yield (bu/ac)</t>
+  </si>
+  <si>
+    <t>Bushels</t>
+  </si>
+  <si>
+    <t>Bushels (ROUND)</t>
+  </si>
+  <si>
+    <t>Willow</t>
+  </si>
+  <si>
+    <t>Ridge</t>
+  </si>
+  <si>
+    <t>Slough</t>
+  </si>
+  <si>
+    <t>Quarter</t>
+  </si>
+  <si>
+    <t>Airport</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Mean yield (AVERAGE)</t>
+  </si>
+  <si>
+    <t>COUNT of fields</t>
+  </si>
+  <si>
+    <t>Weighted average (bu/ac)</t>
+  </si>
+  <si>
+    <t>SUMPRODUCT over SUM</t>
+  </si>
+  <si>
+    <t>The rounded column totals 55,678 -- 0.3 bushels above the unrounded 55,677.7 (Quarter lands on exactly 5,740.5 and rounds up). ROUND changes the stored values, so the total is a sum of rounded numbers; formatting to zero decimals only changes the display, so the column still totals its unrounded values.</t>
+  </si>
+  <si>
+    <t>The weighted average answers it: it counts every bushel once regardless of which field grew it. The plain mean treats each field as equally important, so the small, high-yielding Quarter field counts as much as the large Slough field and pulls the answer up by about 2.3 bu/ac.</t>
+  </si>
+  <si>
+    <t>Part (a)</t>
+  </si>
+  <si>
+    <t>Part (b)</t>
+  </si>
+  <si>
+    <t>Part (c)</t>
+  </si>
+  <si>
+    <t>Part (d)</t>
+  </si>
+  <si>
+    <t>Part (e)</t>
+  </si>
+  <si>
+    <t>Part (f)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="8">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
+        <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D2E9"/>
+        <fgColor rgb="FFD9D2E9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFE2F3"/>
+        <fgColor rgb="FFCFE2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE5CD"/>
+        <fgColor rgb="FFFCE5CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,104 +174,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -467,327 +502,275 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Acres</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Yield (bu/ac)</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Bushels</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Bushels (ROUND)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Willow</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n">
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="4">
         <v>213</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="5">
         <v>52.4</v>
       </c>
       <c r="D2" s="6">
         <f>B2*C2</f>
-        <v/>
+        <v>11161.199999999999</v>
       </c>
       <c r="E2" s="7">
         <f>ROUND(B2*C2,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n">
+        <v>11161</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4">
         <v>147</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="5">
         <v>61.8</v>
       </c>
       <c r="D3" s="6">
         <f>B3*C3</f>
-        <v/>
+        <v>9084.6</v>
       </c>
       <c r="E3" s="7">
         <f>ROUND(B3*C3,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Slough</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
+        <v>9085</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="4">
         <v>326</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="5">
         <v>47.9</v>
       </c>
       <c r="D4" s="6">
         <f>B4*C4</f>
-        <v/>
+        <v>15615.4</v>
       </c>
       <c r="E4" s="7">
         <f>ROUND(B4*C4,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Quarter</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
+        <v>15615</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="4">
         <v>89</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="5">
         <v>64.5</v>
       </c>
       <c r="D5" s="6">
         <f>B5*C5</f>
-        <v/>
+        <v>5740.5</v>
       </c>
       <c r="E5" s="7">
         <f>ROUND(B5*C5,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Airport</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
+        <v>5741</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="4">
         <v>255</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="5">
         <v>55.2</v>
       </c>
       <c r="D6" s="6">
         <f>B6*C6</f>
-        <v/>
+        <v>14076</v>
       </c>
       <c r="E6" s="7">
         <f>ROUND(B6*C6,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
+        <v>14076</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="B7" s="8">
         <f>SUM(B2:B6)</f>
-        <v/>
+        <v>1030</v>
       </c>
       <c r="D7" s="6">
         <f>SUM(D2:D6)</f>
-        <v/>
+        <v>55677.7</v>
       </c>
       <c r="E7" s="7">
         <f>SUM(E2:E6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Mean yield (AVERAGE)</t>
-        </is>
+        <v>55678</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="9" t="s">
+        <v>11</v>
       </c>
       <c r="B9" s="10">
         <f>AVERAGE(C2:C6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>COUNT of fields</t>
-        </is>
+        <v>56.36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="9" t="s">
+        <v>12</v>
       </c>
       <c r="B10" s="9">
         <f>COUNT(C2:C6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>Weighted average (bu/ac)</t>
-        </is>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="11" t="s">
+        <v>13</v>
       </c>
       <c r="B11" s="12">
         <f>D7/B7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>SUMPRODUCT over SUM</t>
-        </is>
+        <v>54.056019417475724</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="13" t="s">
+        <v>14</v>
       </c>
       <c r="B12" s="14">
         <f>SUMPRODUCT(C2:C6,B2:B6)/SUM(B2:B6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>The rounded column totals 55,678 -- 0.3 bushels above the unrounded 55,677.7 (Quarter lands on exactly 5,740.5 and rounds up). ROUND changes the stored values, so the total is a sum of rounded numbers; formatting to zero decimals only changes the display, so the column still totals its unrounded values.</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="16" t="n"/>
-      <c r="H14" s="16" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="n"/>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
-      <c r="G15" s="16" t="n"/>
-      <c r="H15" s="16" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="n"/>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="16" t="n"/>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="16" t="n"/>
-      <c r="G16" s="16" t="n"/>
-      <c r="H16" s="16" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>The weighted average answers it: it counts every bushel once regardless of which field grew it. The plain mean treats each field as equally important, so the small, high-yielding Quarter field counts as much as the large Slough field and pulls the answer up by about 2.3 bu/ac.</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="n"/>
-      <c r="C18" s="18" t="n"/>
-      <c r="D18" s="18" t="n"/>
-      <c r="E18" s="18" t="n"/>
-      <c r="F18" s="18" t="n"/>
-      <c r="G18" s="18" t="n"/>
-      <c r="H18" s="18" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="n"/>
-      <c r="B19" s="18" t="n"/>
-      <c r="C19" s="18" t="n"/>
-      <c r="D19" s="18" t="n"/>
-      <c r="E19" s="18" t="n"/>
-      <c r="F19" s="18" t="n"/>
-      <c r="G19" s="18" t="n"/>
-      <c r="H19" s="18" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="n"/>
-      <c r="B20" s="18" t="n"/>
-      <c r="C20" s="18" t="n"/>
-      <c r="D20" s="18" t="n"/>
-      <c r="E20" s="18" t="n"/>
-      <c r="F20" s="18" t="n"/>
-      <c r="G20" s="18" t="n"/>
-      <c r="H20" s="18" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>Part (a)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>Part (b)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>Part (c)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>Part (d)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>Part (e)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>Part (f)</t>
-        </is>
+        <v>54.056019417475724</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="21"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="21"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="16" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
